--- a/bcmc-vrphd/data/instances/medium_n10_k5.xlsx
+++ b/bcmc-vrphd/data/instances/medium_n10_k5.xlsx
@@ -8923,7 +8923,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -9078,7 +9078,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>237</v>
+        <v>239.5</v>
       </c>
     </row>
     <row r="3">
@@ -9102,7 +9102,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>349.7</v>
+        <v>352.7</v>
       </c>
     </row>
     <row r="6">
